--- a/www/download/IND.abstract_labour.emp.s.mv.WIOD16.xlsx
+++ b/www/download/IND.abstract_labour.emp.s.mv.WIOD16.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>16299.716</t>
+          <t>16299715807.6141</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>16335.968</t>
+          <t>16335967789.5137</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>16569.644</t>
+          <t>16569644025.4306</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>16822.948</t>
+          <t>16822947791.403</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>17474.181</t>
+          <t>17474181336.9007</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>17968.639</t>
+          <t>17968638972.7294</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>18559.812</t>
+          <t>18559811529.9806</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>18932.143</t>
+          <t>18932143175.2364</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>18639.808</t>
+          <t>18639807834.6647</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>19470.337</t>
+          <t>19470337388.6254</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>19481.323</t>
+          <t>19481323398.01</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>20027.955</t>
+          <t>20027955446.187</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>20052.977</t>
+          <t>20052976540.8221</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>20298.753</t>
+          <t>20298752939.957</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>20592.778</t>
+          <t>20592777973.4083</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6252.768</t>
+          <t>6252767994.8565</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6275.861</t>
+          <t>6275860810.76853</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>6246.788</t>
+          <t>6246788020.65491</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>6261.408</t>
+          <t>6261408128.90487</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>6328.953</t>
+          <t>6328953176.89696</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>6364.899</t>
+          <t>6364898649.35328</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>6419.74</t>
+          <t>6419739543.42461</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>6530.27</t>
+          <t>6530270237.83842</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>6670.72</t>
+          <t>6670719886.31428</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>6462.196</t>
+          <t>6462196298.34405</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>6497.797</t>
+          <t>6497796868.58755</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>6597.917</t>
+          <t>6597916680.46395</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>6618.083</t>
+          <t>6618082899.76405</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>6605.721</t>
+          <t>6605720772.61275</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>6656.959</t>
+          <t>6656959460.65489</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5976.432</t>
+          <t>5976431858.10185</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6038.386</t>
+          <t>6038385832.92602</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>6005.793</t>
+          <t>6005792637.02126</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>6003.316</t>
+          <t>6003316274.55024</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>6066.013</t>
+          <t>6066013082.7093</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>6138.331</t>
+          <t>6138330630.56357</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>6217.963</t>
+          <t>6217962958.28666</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>6338.011</t>
+          <t>6338011195.62639</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>6436.824</t>
+          <t>6436824068.35747</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>6338.167</t>
+          <t>6338166753.11412</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>6370.07</t>
+          <t>6370069573.22985</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>6509.268</t>
+          <t>6509267898.55738</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>6537.069</t>
+          <t>6537069392.21542</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>6506.505</t>
+          <t>6506505378.41969</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>6531.333</t>
+          <t>6531333284.32484</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5668.832</t>
+          <t>5668832342.70696</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5712.087</t>
+          <t>5712086837.68754</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5724.447</t>
+          <t>5724446866.23941</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>5810.215</t>
+          <t>5810215437.61124</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>5951.245</t>
+          <t>5951245186.61941</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>5982.292</t>
+          <t>5982291723.23963</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>6194.355</t>
+          <t>6194354813.27753</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>6404.473</t>
+          <t>6404473002.73555</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>6723.273</t>
+          <t>6723272743.95695</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>6404.128</t>
+          <t>6404127963.18293</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>6105.093</t>
+          <t>6105093118.78332</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>5941.915</t>
+          <t>5941915360.94779</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>5759.768</t>
+          <t>5759768081.97418</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>5754.132</t>
+          <t>5754132156.44117</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>5962.96</t>
+          <t>5962960188.28848</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>175462.81</t>
+          <t>175462810262.691</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>177780.558</t>
+          <t>177780557813.654</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>185774.53</t>
+          <t>185774529698.711</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>187182.611</t>
+          <t>187182610836.086</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>195734.938</t>
+          <t>195734938152.806</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>200573.726</t>
+          <t>200573725591.732</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>203337.135</t>
+          <t>203337135024.83</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>207749.264</t>
+          <t>207749264495.325</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>211668.081</t>
+          <t>211668080600.449</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>212019.953</t>
+          <t>212019952627.155</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>211757.907</t>
+          <t>211757906646.478</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>214605.695</t>
+          <t>214605695250.268</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>217748.762</t>
+          <t>217748761779.933</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>220932.438</t>
+          <t>220932437650.183</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>222764.588</t>
+          <t>222764587515.086</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>26666.831</t>
+          <t>26666830726.5914</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>26839.923</t>
+          <t>26839923332.7001</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>27343.82</t>
+          <t>27343820198.5812</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>27813.608</t>
+          <t>27813607710.351</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>28427.011</t>
+          <t>28427010914.3314</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>28745.197</t>
+          <t>28745197280.4661</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>29156.508</t>
+          <t>29156507763.893</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>29811.526</t>
+          <t>29811526203.176</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>30502.659</t>
+          <t>30502658518.3738</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>28685.386</t>
+          <t>28685386391.8636</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>29309.432</t>
+          <t>29309432020.3899</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>29536.526</t>
+          <t>29536526083.382</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>30157.455</t>
+          <t>30157455185.4049</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>30448.512</t>
+          <t>30448511562.1443</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>31622.001</t>
+          <t>31622001097.275</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1281154.752</t>
+          <t>1281154752206.01</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1358661.991</t>
+          <t>1358661990589.66</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1430092.97</t>
+          <t>1430092969802.58</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1472458.079</t>
+          <t>1472458078520.36</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1501021.793</t>
+          <t>1501021793160.33</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1509876.006</t>
+          <t>1509876005638.66</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1494135.694</t>
+          <t>1494135693822.33</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1519893.748</t>
+          <t>1519893747974.16</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1568479.449</t>
+          <t>1568479448756.43</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1591354.705</t>
+          <t>1591354704670.79</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1597046.567</t>
+          <t>1597046566584.14</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1736502.387</t>
+          <t>1736502387336.04</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1770099.919</t>
+          <t>1770099919453.61</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>1784985.375</t>
+          <t>1784985374665.7</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>1790192.448</t>
+          <t>1790192447816.32</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>555.556</t>
+          <t>555556242.970919</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>570.023</t>
+          <t>570023427.894466</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>575.897</t>
+          <t>575896979.567662</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>609.003</t>
+          <t>609002916.645095</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>609.513</t>
+          <t>609513318.417661</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>620.186</t>
+          <t>620186207.799252</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>637.213</t>
+          <t>637213172.101122</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>658.994</t>
+          <t>658994487.580266</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>687.691</t>
+          <t>687690966.878056</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>685.484</t>
+          <t>685483539.768268</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>654.219</t>
+          <t>654219114.287671</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>648.912</t>
+          <t>648911877.178525</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>623.683</t>
+          <t>623683069.56722</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>584.262</t>
+          <t>584262131.77472</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>569.793</t>
+          <t>569793363.988517</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8809.001</t>
+          <t>8809001224.2778</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>8373.354</t>
+          <t>8373354448.47941</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>8393.93</t>
+          <t>8393930062.8032</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>8259.118</t>
+          <t>8259118054.19751</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>8336.588</t>
+          <t>8336587532.54569</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>8524.689</t>
+          <t>8524689306.71469</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>8567.291</t>
+          <t>8567290901.21437</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>8728.184</t>
+          <t>8728183595.10938</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>8932.223</t>
+          <t>8932222935.18434</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>8753.092</t>
+          <t>8753091513.55203</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>8772.629</t>
+          <t>8772628917.64785</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>8794.115</t>
+          <t>8794114976.33455</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>8770.942</t>
+          <t>8770942322.6599</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>8781.362</t>
+          <t>8781361944.37269</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>8846.175</t>
+          <t>8846175028.06073</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>54230.834</t>
+          <t>54230834365.3405</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>53816.067</t>
+          <t>53816066786.0133</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>53261.028</t>
+          <t>53261028438.1409</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>52441.828</t>
+          <t>52441827984.2541</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>52425.683</t>
+          <t>52425683060.2941</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>52007.014</t>
+          <t>52007013720.6426</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>53236.784</t>
+          <t>53236783785.796</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>54300.962</t>
+          <t>54300961886.0936</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>54743.133</t>
+          <t>54743132783.1866</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>52783.931</t>
+          <t>52783930767.4069</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>53743.088</t>
+          <t>53743087707.4673</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>54658.328</t>
+          <t>54658328155.3105</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>54707.034</t>
+          <t>54707033600.2079</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>54610.75</t>
+          <t>54610750441.0103</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>55404.125</t>
+          <t>55404124702.9855</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3941.134</t>
+          <t>3941134337.12402</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3985.871</t>
+          <t>3985870692.32848</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>3958.902</t>
+          <t>3958902157.13691</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>3907.52</t>
+          <t>3907520394.17614</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>3886.552</t>
+          <t>3886551867.86201</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>3939.068</t>
+          <t>3939067538.55247</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>4041.838</t>
+          <t>4041838223.71621</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>4083.314</t>
+          <t>4083314218.58938</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>4133.763</t>
+          <t>4133763067.15041</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>3986.916</t>
+          <t>3986916422.04031</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>3872.712</t>
+          <t>3872711856.43258</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>3917.698</t>
+          <t>3917698340.49</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>3853.532</t>
+          <t>3853532079.7049</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>3914.671</t>
+          <t>3914670611.82118</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>3951.917</t>
+          <t>3951916620.33987</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>28651.032</t>
+          <t>28651032237.5724</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>29812.188</t>
+          <t>29812187570.0757</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>30680.005</t>
+          <t>30680005177.9707</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>31482.397</t>
+          <t>31482397040.4979</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>32390.788</t>
+          <t>32390788310.4722</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>33471.927</t>
+          <t>33471927313.7018</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>34629.169</t>
+          <t>34629169289.1684</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>35477.601</t>
+          <t>35477600508.5355</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>35675.77</t>
+          <t>35675770088.3706</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>33590.325</t>
+          <t>33590324518.032</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>32842.848</t>
+          <t>32842847841.9665</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>32027.736</t>
+          <t>32027736197.5015</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>30425.323</t>
+          <t>30425322762.6033</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>29371.932</t>
+          <t>29371931522.7992</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>29690.137</t>
+          <t>29690136769.5273</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1145.697</t>
+          <t>1145697241.31722</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1154.004</t>
+          <t>1154004055.62888</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1147.224</t>
+          <t>1147223750.30331</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1188.425</t>
+          <t>1188425337.35316</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1187.862</t>
+          <t>1187862408.57165</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1236.342</t>
+          <t>1236341694.4304</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1287.935</t>
+          <t>1287935156.40906</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>1290.606</t>
+          <t>1290606232.73379</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>1267.15</t>
+          <t>1267149755.34013</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1064.285</t>
+          <t>1064284595.31066</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1031.077</t>
+          <t>1031076619.31007</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1127.48</t>
+          <t>1127480340.86792</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1105.17</t>
+          <t>1105169984.73503</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>1127.236</t>
+          <t>1127235991.6808</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>1148.028</t>
+          <t>1148028016.49595</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3796.818</t>
+          <t>3796817893.47852</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3824.68</t>
+          <t>3824679951.63623</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>3846.687</t>
+          <t>3846687358.50518</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>3838.259</t>
+          <t>3838258654.91951</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>3860.534</t>
+          <t>3860534423.86954</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>3900.848</t>
+          <t>3900847529.80908</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>3971.21</t>
+          <t>3971209679.26154</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>4053.846</t>
+          <t>4053846161.8182</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>4138.324</t>
+          <t>4138323946.24825</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>3979.886</t>
+          <t>3979885985.69808</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>3974.002</t>
+          <t>3974002234.9397</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>4028.196</t>
+          <t>4028195906.3542</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>4031.242</t>
+          <t>4031241507.96132</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>3986.833</t>
+          <t>3986832756.21399</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>3963.49</t>
+          <t>3963490159.26814</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>36942.169</t>
+          <t>36942169003.0818</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>37340.115</t>
+          <t>37340114823.252</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>36641.344</t>
+          <t>36641343945.7132</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>36570.573</t>
+          <t>36570572791.9737</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>37323.374</t>
+          <t>37323374308.4042</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>37483.283</t>
+          <t>37483283324.8983</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>37330.401</t>
+          <t>37330400965.5017</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>38311.492</t>
+          <t>38311491992.6367</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>38757.878</t>
+          <t>38757878362.7045</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>37873.733</t>
+          <t>37873733059.2841</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>38048.975</t>
+          <t>38048974568.8174</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>38433.573</t>
+          <t>38433572933.6238</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>38427.711</t>
+          <t>38427710726.4551</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>38056.003</t>
+          <t>38056002537.057</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>38131.699</t>
+          <t>38131698985.7674</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>45942.081</t>
+          <t>45942081317.6658</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>46316.584</t>
+          <t>46316583936.9278</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>46337.779</t>
+          <t>46337778671.5812</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>46526.438</t>
+          <t>46526438498.5265</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>46579.213</t>
+          <t>46579212759.3678</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>47672.921</t>
+          <t>47672921228.5797</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>48018.735</t>
+          <t>48018735318.0445</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>48556.582</t>
+          <t>48556582008.6673</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>48349.912</t>
+          <t>48349911573.3506</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>47596.655</t>
+          <t>47596654590.3695</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>47795.13</t>
+          <t>47795129925.2147</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>48075.43</t>
+          <t>48075430462.1808</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>49129.723</t>
+          <t>49129722694.0578</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>49988.879</t>
+          <t>49988879413.4637</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>51360.176</t>
+          <t>51360176081.6999</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>8733.793</t>
+          <t>8733792982.43389</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>8744.552</t>
+          <t>8744551595.55054</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>8938.064</t>
+          <t>8938063789.37469</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>9052.748</t>
+          <t>9052747770.11624</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>9228.506</t>
+          <t>9228505989.84124</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>9814.808</t>
+          <t>9814808490.6709</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>9900.977</t>
+          <t>9900977076.97954</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>10052.118</t>
+          <t>10052117686.2983</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>10122.079</t>
+          <t>10122078805.7629</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>9982.986</t>
+          <t>9982986459.87159</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>9297.616</t>
+          <t>9297616177.50601</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>8652.106</t>
+          <t>8652106004.09944</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>8042.358</t>
+          <t>8042357542.78347</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>7729.316</t>
+          <t>7729315520.0255</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>7625.096</t>
+          <t>7625096110.78841</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>8478.118</t>
+          <t>8478117556.81902</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>8303.851</t>
+          <t>8303851454.25828</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>8347.633</t>
+          <t>8347632976.7416</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>8224.11</t>
+          <t>8224109984.81019</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>8273.34</t>
+          <t>8273340121.49415</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>8293.71</t>
+          <t>8293710470.47457</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>8312.569</t>
+          <t>8312568916.01426</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>8286.024</t>
+          <t>8286023714.99105</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>8132.385</t>
+          <t>8132385075.48112</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>7861.527</t>
+          <t>7861526875.1604</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>7012.817</t>
+          <t>7012816958.62474</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>6995.249</t>
+          <t>6995249483.01401</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>6927.549</t>
+          <t>6927549280.15119</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>6974.654</t>
+          <t>6974653781.212</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>7336.303</t>
+          <t>7336303264.66647</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>159660.176</t>
+          <t>159660176212.213</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>165538.318</t>
+          <t>165538317824.663</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>176488.77</t>
+          <t>176488769880.351</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>185008.412</t>
+          <t>185008412128.888</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>194145.927</t>
+          <t>194145927287.217</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>166608.509</t>
+          <t>166608508721.801</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>155857.243</t>
+          <t>155857242502.896</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>157350.939</t>
+          <t>157350939471.152</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>159747.607</t>
+          <t>159747607028.538</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>162810.544</t>
+          <t>162810543957.806</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>169976.613</t>
+          <t>169976613195.317</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>173429.409</t>
+          <t>173429409357.288</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>190651.007</t>
+          <t>190651006689.069</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>212782.301</t>
+          <t>212782301329.899</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>237573.657</t>
+          <t>237573657268.388</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>946052.946</t>
+          <t>946052945525.205</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>973681.83</t>
+          <t>973681830093.161</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1002443.878</t>
+          <t>1002443878447.26</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1033812.503</t>
+          <t>1033812502511.78</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1068802.725</t>
+          <t>1068802725066.67</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1077779.934</t>
+          <t>1077779934232.21</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>1077119.508</t>
+          <t>1077119507853.15</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>1078735.397</t>
+          <t>1078735396947.16</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>1080383.099</t>
+          <t>1080383099414.01</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1084735.105</t>
+          <t>1084735105192.72</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1096986.716</t>
+          <t>1096986716367.36</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1116767.369</t>
+          <t>1116767368795.53</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1274604.663</t>
+          <t>1274604662813.14</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>1438109.826</t>
+          <t>1438109826441.88</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>1557808.828</t>
+          <t>1557808827706.56</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3226.327</t>
+          <t>3226327064.12101</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3310.464</t>
+          <t>3310463794.58961</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>3323.682</t>
+          <t>3323681675.52388</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>3359.551</t>
+          <t>3359551162.43036</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>3455.104</t>
+          <t>3455104397.87236</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>3642.632</t>
+          <t>3642632007.33466</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>3805.262</t>
+          <t>3805262296.71422</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>3942.466</t>
+          <t>3942466357.59309</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>3875.257</t>
+          <t>3875256745.09768</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>3502.182</t>
+          <t>3502182283.7692</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>3330.611</t>
+          <t>3330611463.89694</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>3276.519</t>
+          <t>3276519093.18294</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>3268.551</t>
+          <t>3268550890.99011</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>3364.626</t>
+          <t>3364626004.36484</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>3429.051</t>
+          <t>3429051263.54074</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>39420.189</t>
+          <t>39420189153.1113</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>39936.347</t>
+          <t>39936347436.3307</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>40264.378</t>
+          <t>40264377670.1278</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>40403.117</t>
+          <t>40403116557.3606</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>40766.721</t>
+          <t>40766720974.8105</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>40687.65</t>
+          <t>40687649681.6286</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>41694.096</t>
+          <t>41694095921.8949</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>42227.49</t>
+          <t>42227489839.6732</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>42385.025</t>
+          <t>42385025395.2026</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>40818.254</t>
+          <t>40818253992.5964</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>40514.528</t>
+          <t>40514527626.6537</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>40619.552</t>
+          <t>40619551575.538</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>39574.135</t>
+          <t>39574134542.2686</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>38497.084</t>
+          <t>38497083824.1301</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>38582.425</t>
+          <t>38582424798.4972</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>119243.178</t>
+          <t>119243177528.611</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>117456.865</t>
+          <t>117456864760.35</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>114587.472</t>
+          <t>114587472329.208</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>114337.246</t>
+          <t>114337245779.594</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>114700.225</t>
+          <t>114700224883.941</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>114245.012</t>
+          <t>114245012397.374</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>115079.656</t>
+          <t>115079655742.997</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>115249.215</t>
+          <t>115249214671.485</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>113633.208</t>
+          <t>113633208138.101</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>108862.472</t>
+          <t>108862472009.081</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>109633.813</t>
+          <t>109633812578.106</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>108990.363</t>
+          <t>108990363467.158</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>109076.429</t>
+          <t>109076429086.599</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>108181.505</t>
+          <t>108181505268.47</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>106612.053</t>
+          <t>106612052983.583</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>42750.118</t>
+          <t>42750118052.9724</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>43320.434</t>
+          <t>43320433560.2392</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>44448.234</t>
+          <t>44448234160.0989</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>44999.902</t>
+          <t>44999901787.586</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>47760.951</t>
+          <t>47760951219.9437</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>46490.768</t>
+          <t>46490767592.7929</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>47124.278</t>
+          <t>47124278307.1451</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>46208.376</t>
+          <t>46208375887.9648</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>46206.822</t>
+          <t>46206822119.9894</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>48314.738</t>
+          <t>48314738145.4579</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>48435.659</t>
+          <t>48435658895.2367</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>49623.627</t>
+          <t>49623627490.1896</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>49515.417</t>
+          <t>49515417484.7972</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>51651.61</t>
+          <t>51651610118.9387</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>52079.928</t>
+          <t>52079928290.3435</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2612.717</t>
+          <t>2612717112.75203</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2505.268</t>
+          <t>2505267774.01068</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2559.502</t>
+          <t>2559502143.84006</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2643.032</t>
+          <t>2643032104.95401</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2657.404</t>
+          <t>2657404373.91654</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2693.83</t>
+          <t>2693829793.28363</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2735.9</t>
+          <t>2735899649.98004</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2771.906</t>
+          <t>2771906228.64831</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2744.239</t>
+          <t>2744239188.51545</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2441.381</t>
+          <t>2441381463.19636</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2340.933</t>
+          <t>2340932948.15619</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>2319.569</t>
+          <t>2319568680.19385</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2359.055</t>
+          <t>2359055474.33635</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>2372.141</t>
+          <t>2372140632.9818</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2406.942</t>
+          <t>2406941853.2429</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>421.127</t>
+          <t>421127195.902182</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>442.933</t>
+          <t>442933013.511344</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>454.953</t>
+          <t>454953488.490295</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>462.588</t>
+          <t>462588429.823914</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>472.922</t>
+          <t>472922385.726402</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>478.116</t>
+          <t>478116434.88654</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>496.314</t>
+          <t>496314041.1196</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>521.989</t>
+          <t>521988674.645739</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>546.799</t>
+          <t>546799020.817577</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>534.89</t>
+          <t>534889806.986626</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>546.02</t>
+          <t>546019585.474889</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>561.799</t>
+          <t>561799096.770344</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>572.337</t>
+          <t>572336833.679586</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>585.278</t>
+          <t>585277822.109048</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>610.41</t>
+          <t>610410441.856384</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1816.292</t>
+          <t>1816292291.87544</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1860.284</t>
+          <t>1860283855.90591</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1859.229</t>
+          <t>1859229190.25067</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1866.59</t>
+          <t>1866589980.09179</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1826.228</t>
+          <t>1826227658.35436</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1855.1</t>
+          <t>1855100471.26879</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1967.37</t>
+          <t>1967370406.58059</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>1998.781</t>
+          <t>1998781034.76197</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2103.105</t>
+          <t>2103105484.46315</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1750.493</t>
+          <t>1750493218.35106</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1610.913</t>
+          <t>1610913462.84186</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1645.547</t>
+          <t>1645546655.14667</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1690.105</t>
+          <t>1690104996.0454</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>1714.481</t>
+          <t>1714480902.3765</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>1723.085</t>
+          <t>1723085246.24906</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>67764.535</t>
+          <t>67764535433.6991</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>66516.442</t>
+          <t>66516442119.8142</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>66853.296</t>
+          <t>66853296093.0024</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>70413.953</t>
+          <t>70413952732.8604</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>73379.424</t>
+          <t>73379424202.5116</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>73758.407</t>
+          <t>73758406520.8177</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>76765.912</t>
+          <t>76765912043.6864</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>78827.94</t>
+          <t>78827939848.0456</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>80011.524</t>
+          <t>80011524485.7955</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>77833.22</t>
+          <t>77833219858.3709</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>79252.704</t>
+          <t>79252704288.2223</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>80303.237</t>
+          <t>80303237474.0902</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>82882.043</t>
+          <t>82882043350.6905</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>82579.654</t>
+          <t>82579653610.9187</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>83500.643</t>
+          <t>83500643021.8915</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>320.074</t>
+          <t>320073857.17253</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>306.075</t>
+          <t>306074988.057252</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>317400093.591664</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>317.916</t>
+          <t>317915576.174024</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>300.648</t>
+          <t>300648075.275399</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>318.199</t>
+          <t>318199461.444798</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>316.823</t>
+          <t>316822523.113489</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>327.82</t>
+          <t>327820419.918699</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>349.132</t>
+          <t>349132074.765234</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>346.397</t>
+          <t>346396798.387206</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>350.083</t>
+          <t>350082663.587555</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>343.938</t>
+          <t>343937687.325305</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>348.914</t>
+          <t>348913662.255641</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>350.831</t>
+          <t>350830684.044455</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>360.464</t>
+          <t>360464010.654467</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>11359.31</t>
+          <t>11359309805.3968</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>11536.985</t>
+          <t>11536984784.9073</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>11527.464</t>
+          <t>11527464474.2725</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>11416.07</t>
+          <t>11416069586.2901</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>11436.65</t>
+          <t>11436649900.8717</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>11369.142</t>
+          <t>11369142288.8029</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>11548.882</t>
+          <t>11548881521.0916</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>11858.613</t>
+          <t>11858613200.2748</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>12084.615</t>
+          <t>12084615018.4165</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>11903.64</t>
+          <t>11903640320.4526</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>11799.267</t>
+          <t>11799266902.2646</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>11925.13</t>
+          <t>11925129906.3241</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>11821.412</t>
+          <t>11821411568.8831</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>11761.382</t>
+          <t>11761382227.1958</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>11751.396</t>
+          <t>11751395682.6649</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>30998.699</t>
+          <t>30998698763.2451</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>30957.757</t>
+          <t>30957756871.4674</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>29072.771</t>
+          <t>29072771252.9655</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>28387.481</t>
+          <t>28387481007.8656</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>28743.737</t>
+          <t>28743736927.1674</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>29246.32</t>
+          <t>29246319666.1798</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>30115.669</t>
+          <t>30115669461.865</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>31356.249</t>
+          <t>31356249463.2502</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>32444.88</t>
+          <t>32444880152.158</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>32228.957</t>
+          <t>32228957491.3467</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>31410.397</t>
+          <t>31410396586.2368</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>31414.157</t>
+          <t>31414157074.4263</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>31319.402</t>
+          <t>31319401589.6173</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>31276.043</t>
+          <t>31276043269.1026</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>31527.743</t>
+          <t>31527742814.0696</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>9642.583</t>
+          <t>9642582610.33032</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>9761.2</t>
+          <t>9761200128.4371</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>9745.748</t>
+          <t>9745748193.27666</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>9632.705</t>
+          <t>9632704872.87154</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>9591.538</t>
+          <t>9591537537.01811</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>9540.612</t>
+          <t>9540612066.78759</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>9542.568</t>
+          <t>9542568448.17543</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>9552.257</t>
+          <t>9552256680.27624</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>9517.419</t>
+          <t>9517419005.94107</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>9287.535</t>
+          <t>9287534971.61034</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>9196.015</t>
+          <t>9196015297.90082</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>8913.526</t>
+          <t>8913526077.68065</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>8477.996</t>
+          <t>8477995575.09781</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>8310.859</t>
+          <t>8310859376.14855</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>8496.028</t>
+          <t>8496028440.77597</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>20661.817</t>
+          <t>20661817175.4686</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>20587.813</t>
+          <t>20587813032.999</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>18217.555</t>
+          <t>18217554631.8914</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>18612.148</t>
+          <t>18612148360.5748</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>18234.078</t>
+          <t>18234077586.351</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>17993.604</t>
+          <t>17993604439.9295</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>17880.91</t>
+          <t>17880909758.4704</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>18146.449</t>
+          <t>18146449122.605</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>17925.126</t>
+          <t>17925126035.0482</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>17592.821</t>
+          <t>17592820564.6853</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>17407.229</t>
+          <t>17407229096.2659</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>17693.624</t>
+          <t>17693624259.7554</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>14453.559</t>
+          <t>14453558936.3407</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>14325.894</t>
+          <t>14325893689.5371</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>14814.339</t>
+          <t>14814339315.0406</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>136541.52</t>
+          <t>136541520147.878</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>136046.652</t>
+          <t>136046652027.818</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>136983.091</t>
+          <t>136983090752.447</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>138344.327</t>
+          <t>138344327273.116</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>139714.335</t>
+          <t>139714334716.223</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>141561.856</t>
+          <t>141561856367.585</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>143026.816</t>
+          <t>143026815632.393</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>144464.258</t>
+          <t>144464258014.926</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>138811.358</t>
+          <t>138811357515.703</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>134351.527</t>
+          <t>134351526696.895</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>135336.087</t>
+          <t>135336087079.63</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>134430.087</t>
+          <t>134430087458.914</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>136550.786</t>
+          <t>136550785577.677</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>133217.91</t>
+          <t>133217909534.563</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>132151.049</t>
+          <t>132151049460.07</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>3497.542</t>
+          <t>3497541772.78546</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3501.492</t>
+          <t>3501492497.90148</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>3406.647</t>
+          <t>3406647308.54267</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>3335.265</t>
+          <t>3335265229.60849</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>3412.14</t>
+          <t>3412140476.36069</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>3529.301</t>
+          <t>3529300675.50771</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>3606.48</t>
+          <t>3606480451.78643</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>3699.132</t>
+          <t>3699132079.45275</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>3837.944</t>
+          <t>3837944163.7089</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>3720.763</t>
+          <t>3720762792.72847</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>3733.664</t>
+          <t>3733664494.60078</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>3771.814</t>
+          <t>3771813748.64838</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>3765.412</t>
+          <t>3765412498.17778</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>3701.243</t>
+          <t>3701242694.88282</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>3732.752</t>
+          <t>3732752350.90171</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1460.319</t>
+          <t>1460318926.67031</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1452.745</t>
+          <t>1452745165.57945</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>1520.947</t>
+          <t>1520946700.18349</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1524.644</t>
+          <t>1524643555.18188</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1554.983</t>
+          <t>1554983028.24434</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1512.181</t>
+          <t>1512181466.57251</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>1515.366</t>
+          <t>1515366288.85154</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>1554.456</t>
+          <t>1554455877.69895</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>1608.306</t>
+          <t>1608306156.30953</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>1594.986</t>
+          <t>1594985639.75174</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1578.754</t>
+          <t>1578753822.09547</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1537.495</t>
+          <t>1537495074.62847</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1494.105</t>
+          <t>1494105322.78378</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>1495.012</t>
+          <t>1495011981.6391</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>1528.746</t>
+          <t>1528746046.16553</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>7027.639</t>
+          <t>7027638752.30506</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>7088.821</t>
+          <t>7088820907.90552</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>6972.452</t>
+          <t>6972451916.59847</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>6866.041</t>
+          <t>6866041376.57185</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>6936.24</t>
+          <t>6936239896.99215</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>6919.239</t>
+          <t>6919239031.76567</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>7032.312</t>
+          <t>7032312492.87729</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>7240.66</t>
+          <t>7240660094.87832</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>7337.915</t>
+          <t>7337915318.68694</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>7133.265</t>
+          <t>7133264592.96264</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>7321.502</t>
+          <t>7321501540.79612</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>7452.903</t>
+          <t>7452902959.09643</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>7444.999</t>
+          <t>7444999377.16936</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>7487.874</t>
+          <t>7487873870.34087</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>7614.259</t>
+          <t>7614258833.87482</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>44566.468</t>
+          <t>44566468240.5365</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>44561.229</t>
+          <t>44561228769.3933</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>42519.449</t>
+          <t>42519448969.283</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>41699.231</t>
+          <t>41699231172.2026</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>42223.767</t>
+          <t>42223767337.2428</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>42900.567</t>
+          <t>42900567013.1925</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>41391.622</t>
+          <t>41391622196.0747</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>39982.934</t>
+          <t>39982933638.3123</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>40627.392</t>
+          <t>40627391548.6242</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>40617.937</t>
+          <t>40617937004.5503</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>43006.312</t>
+          <t>43006311701.3585</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>45707.039</t>
+          <t>45707038614.23</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>49822.229</t>
+          <t>49822228973.3588</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>54323.515</t>
+          <t>54323515491.3295</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>60812.638</t>
+          <t>60812637696.3403</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>36696.374</t>
+          <t>36696373692.474</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>35770.452</t>
+          <t>35770451509.648</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>38234.799</t>
+          <t>38234799285.1855</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>38292.743</t>
+          <t>38292742644.1067</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>38946.251</t>
+          <t>38946251138.5658</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>39321.375</t>
+          <t>39321374802.2346</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>40260.13</t>
+          <t>40260130337.1378</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>40600.85</t>
+          <t>40600849854.4912</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>39997.486</t>
+          <t>39997485898.1932</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>40087.459</t>
+          <t>40087459438.6781</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>41586.89</t>
+          <t>41586890313.957</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>40801.467</t>
+          <t>40801467380.6395</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>41456.613</t>
+          <t>41456612777.3244</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>41808.076</t>
+          <t>41808075896.1437</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>41977.788</t>
+          <t>41977788379.1441</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>267851.122</t>
+          <t>267851121690.988</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>266794.928</t>
+          <t>266794928420.605</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>263860.736</t>
+          <t>263860736403.136</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>261972.505</t>
+          <t>261972504587.059</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>264921.645</t>
+          <t>264921644691.804</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>269187.999</t>
+          <t>269187998859.722</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>274200.86</t>
+          <t>274200860236.142</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>275901.354</t>
+          <t>275901353845.2</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>274104.683</t>
+          <t>274104683346.715</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>260237.659</t>
+          <t>260237659395.632</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>260971.169</t>
+          <t>260971168828.067</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>264895.492</t>
+          <t>264895491592.929</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>269975.963</t>
+          <t>269975962680.956</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>274801.011</t>
+          <t>274801011496.567</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>280476.1</t>
+          <t>280476100217.87</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1749326.228</t>
+          <t>1749326227674.04</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1823779.121</t>
+          <t>1823779120993.5</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>1894668.559</t>
+          <t>1894668558535.74</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1972878.065</t>
+          <t>1972878064906.69</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2061628.419</t>
+          <t>2061628418959.29</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2095774.127</t>
+          <t>2095774127486.82</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2153261.884</t>
+          <t>2153261884442.65</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2217351.867</t>
+          <t>2217351866773.18</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2290607.861</t>
+          <t>2290607861353.38</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2333155.69</t>
+          <t>2333155690282.16</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2392411.796</t>
+          <t>2392411796388.16</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>2540846.285</t>
+          <t>2540846285389.31</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>2704019.78</t>
+          <t>2704019780088.7</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>2869503.873</t>
+          <t>2869503872990.63</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>3005334.063</t>
+          <t>3005334063447.3</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>5435359.568</t>
+          <t>5435359567899.25</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>5620187.688</t>
+          <t>5620187687870.89</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>5803771.87</t>
+          <t>5803771870469.88</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>5968603.951</t>
+          <t>5968603951483.1</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>6154539.871</t>
+          <t>6154539871462.13</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>6193953.057</t>
+          <t>6193953057225.88</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>6244516.084</t>
+          <t>6244516084436.31</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>6353907.563</t>
+          <t>6353907562550.06</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>6479929.161</t>
+          <t>6479929160659.97</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>6517642.265</t>
+          <t>6517642265291.28</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>6607148.458</t>
+          <t>6607148458378.88</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>6929248.423</t>
+          <t>6929248423114.86</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>7313026.542</t>
+          <t>7313026541991.18</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>7687668.269</t>
+          <t>7687668269104.19</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>7992262.151</t>
+          <t>7992262151012.01</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4337,84 +4342,84 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>3036.893</t>
+          <t>3036892694.32461</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>3001.987</t>
+          <t>3001987215.94689</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>3056.057</t>
+          <t>3056057432.89268</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>3092.179</t>
+          <t>3092178728.78127</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>3137.303</t>
+          <t>3137303428.40601</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>3149.281</t>
+          <t>3149280730.61517</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>3240.171</t>
+          <t>3240170535.52178</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>3310.082</t>
+          <t>3310082419.01299</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>3438.268</t>
+          <t>3438267974.83361</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>3410.056</t>
+          <t>3410056192.26195</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>3294.414</t>
+          <t>3294413844.9414</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>3167.11</t>
+          <t>3167110175.61067</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>3022.4</t>
+          <t>3022399604.83598</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>2923.053</t>
+          <t>2923053341.85277</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2966.935</t>
+          <t>2966935365.30506</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4424,84 +4429,84 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>7403.791</t>
+          <t>7403790883.86285</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>7335.74</t>
+          <t>7335739689.91635</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>7274.751</t>
+          <t>7274750953.336</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>7307.236</t>
+          <t>7307236001.83675</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>7454.801</t>
+          <t>7454801395.14908</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>7494.642</t>
+          <t>7494641544.79047</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>7589.781</t>
+          <t>7589781265.81113</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>7717.644</t>
+          <t>7717644071.29197</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>7866.345</t>
+          <t>7866345152.98363</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>7857.804</t>
+          <t>7857803829.99937</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>7890.129</t>
+          <t>7890128958.4337</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>8045.498</t>
+          <t>8045497538.40311</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>8089.34</t>
+          <t>8089339836.82285</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>8100.645</t>
+          <t>8100644729.34871</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>8210.192</t>
+          <t>8210192468.06948</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4511,84 +4516,84 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>3293.21</t>
+          <t>3293210040.65503</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>3249.445</t>
+          <t>3249444885.27786</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>3223.564</t>
+          <t>3223563931.32518</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>3165.899</t>
+          <t>3165899302.06539</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>3229.615</t>
+          <t>3229614804.47456</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>3280.768</t>
+          <t>3280768157.51993</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>3384.942</t>
+          <t>3384942137.96087</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>3549.279</t>
+          <t>3549279257.00595</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>3672.623</t>
+          <t>3672623155.76729</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>3618.799</t>
+          <t>3618798931.27386</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>3612.94</t>
+          <t>3612940317.49222</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>3685.378</t>
+          <t>3685377759.04541</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>3751.593</t>
+          <t>3751592854.95187</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>3785.21</t>
+          <t>3785210097.90135</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>3830.627</t>
+          <t>3830627170.65573</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4600,7 +4605,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4612,7 +4617,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4624,7 +4629,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4636,7 +4641,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4648,7 +4653,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4695,6 +4700,11 @@
           <t>abstract_labour.emp.s.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4729,6 +4739,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD16</t>
